--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13e9ac170037a33</t>
+          <t>https://www.indeed.com/viewjob?jk=9d078162c8ac8e2b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid, Houston based)</t>
+          <t>Data Scientist with Python expertise in New York</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RectorSeal</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, XGBoost, LightGBM, Redshift, BigQuery, MLflow, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56bf46bcdf3a7d3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7865920d36264a0b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II (Node, React, Typescript)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379e47c9eb6a18e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f19fe0e24c9417c4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Hybrid, Houston based)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABYLIST</t>
+          <t>CSW Industrials</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, AWS SageMaker, MLflow, Kubernetes, GitHub Actions, Terraform, Git, Snowflake, MySQL, SQL</t>
+          <t>RAG, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505a3c300078fdf9</t>
+          <t>https://www.indeed.com/viewjob?jk=53bfcfec62e19f29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, S3, Glue, Redshift, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af1ea243de64d80</t>
+          <t>https://www.indeed.com/viewjob?jk=aa20e78aa361630b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer - Data Platform &amp; Martech Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49d8fecfc03771d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5cb397b1e7e030</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Data Engineer, Engineering Data Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515869f2aba872b</t>
+          <t>https://www.indeed.com/viewjob?jk=391a7c687426739b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62b0f3021eecff3</t>
+          <t>https://www.indeed.com/viewjob?jk=948a2c5f37b820dc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, RAG, Data Lake, Kinesis, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,1407 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182a0644f0db1be9</t>
+          <t>https://www.indeed.com/viewjob?jk=88ee86c32dd547a8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer with Expert-level SQL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c71b20b1e19434b6</t>
+          <t>https://www.indeed.com/viewjob?jk=be322dd8c2436cfd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Lowenstein Sandler</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, S3, Data Lake, CI/CD, Git, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7443df35076432f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist with strong Algorithm experience</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Docker, CI/CD, Hadoop, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6714d23df870368</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a380c35ffe71f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Databricks Developer, SAP S/4 Data Products and Governance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee20fa8ee7d3e166</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Glue, Apache Airflow, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aa1ab37d34c6e8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Digital Advisory | Consultant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Buro Happold</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d2092052db26f0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=870e0d092bfdc635</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=075b3631b7fd3201</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (USA, Remote)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Soulside AI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, EC2, Kinesis, AKS, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad3f3e0423505c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sonora Quest Laboratories</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Azure ML, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908b181e68af5318</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Banner Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Azure ML, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d5ef8294abc2e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Included Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4407cc61ee95e68e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7225159ea5dafd9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c63b9d56f94df8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7de96313bda682b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=949dc07e149530ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Computer Vision Engineer-Edge</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Viatouch Media Inc</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, MLflow, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f7148302e3316ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Generative AI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cc744e38f33256f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer / FrontEnd Engineer, Qualcomm AI SW Stack</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=363d9afb96af951b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core AI Software</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95ff71f1c106957f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b7bc95b3eeb8d40</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer Contractor - Talent Reserve (contract)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, PySpark, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f35a1544e260ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51e94afb6f8a79f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e64b465c8e84bf56</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29dea18cde3fa715</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9940bae2a9c7dc6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ignition Platform Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f264960d10992dc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Capgemini Invent - Contextual Systems Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4aa0383c6ea6e83</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GenAI Software Development Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f6d8b3ddffcbfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer – Google ADK/GCP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TTEC Digital</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5aaa66d5e404832</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a175d65fa4645f9</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03558ae01650be1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2751e712d2e52966</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SCADA Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c3f560305e16d6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior SCADA Engineer - Ignition Platform</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c99fad1f2660ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b25219457e0314cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mochi Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc44245d474ec216</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI and GTM Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43d514bb5b64d772</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI and GTM Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ecf1042f78fc6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spire Orthopedic Partners</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Athena, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ca3daded6ed547</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
+          <t>Generative AI, RAG, Gemini, S3, Glue, Data Lake, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d078162c8ac8e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=62196b8dbe66970e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist with Python expertise in New York</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, XGBoost, LightGBM, Redshift, BigQuery, MLflow, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7865920d36264a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf159ea2d58917</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19fe0e24c9417c4</t>
+          <t>https://www.indeed.com/viewjob?jk=91a211ab014dbb4d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid, Houston based)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSW Industrials</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bfcfec62e19f29</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1f2f31f27654c4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Senior Consultant - Data &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Glue, Redshift, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, LLaMA, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa20e78aa361630b</t>
+          <t>https://www.indeed.com/viewjob?jk=372415265e34d8ed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform &amp; Martech Engineering</t>
+          <t>DevOps Automation Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>Generative AI, RAG, Copilot, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5cb397b1e7e030</t>
+          <t>https://www.indeed.com/viewjob?jk=825f817628cb4742</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Engineering Data Analytics</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Databricks, Redshift, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, FastAPI, CI/CD, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391a7c687426739b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a31dee92110efa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948a2c5f37b820dc</t>
+          <t>https://www.indeed.com/viewjob?jk=852c0e11eed656b7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Microsoft Fabric Expert with Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Kinesis, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Synapse, Data Lake, Dataflow, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,137 +776,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ee86c32dd547a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a226f53d4c7a4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer with Expert-level SQL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift</t>
+          <t>RAG, BigQuery, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be322dd8c2436cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=1140218fae3fb0d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Middle AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lowenstein Sandler</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Data Lake, CI/CD, Git, Power BI, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7443df35076432f</t>
+          <t>https://www.indeed.com/viewjob?jk=280a91e4de3c0c5e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist with strong Algorithm experience</t>
+          <t>AI Enabled Engineer | Columbus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Docker, CI/CD, Hadoop, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6714d23df870368</t>
+          <t>https://www.indeed.com/viewjob?jk=cb8cd25a4e1188c4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, S3, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a380c35ffe71f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff40ea722f15df2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer, SAP S/4 Data Products and Governance</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>OCLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, SQL, R</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee20fa8ee7d3e166</t>
+          <t>https://www.indeed.com/viewjob?jk=b876386d7acb700c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Glue, Apache Airflow, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa1ab37d34c6e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5023af7cec558f8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Digital Advisory | Consultant</t>
+          <t>FullStack Engineer (AWS AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Buro Happold</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2092052db26f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfeac083f625981a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>AI Prompt Engineer(Contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>Generative AI, Prompt Engineering, CI/CD, Jenkins, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870e0d092bfdc635</t>
+          <t>https://www.indeed.com/viewjob?jk=65775bd80e816a3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Synapse, Data Lake, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075b3631b7fd3201</t>
+          <t>https://www.indeed.com/viewjob?jk=855e7c38ba45b423</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer (USA, Remote)</t>
+          <t>Senior AI Scientists</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, EC2, Kinesis, AKS, Terraform, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3f3e0423505c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d265b5cdcb3c247</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Machine Learning Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sonora Quest Laboratories</t>
+          <t>Coding Macaw Bootcamp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure ML, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908b181e68af5318</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5ab97b96d18174</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer II, Search and Recommendations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure ML, GitHub Actions, Git, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d5ef8294abc2e4</t>
+          <t>https://www.indeed.com/viewjob?jk=061f6f2d8cb79161</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II, Search and Recommendations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Included Health</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Python, SQL, R</t>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4407cc61ee95e68e</t>
+          <t>https://www.indeed.com/viewjob?jk=fce26e8abb6b4999</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Core Infrastructure Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,112 +1256,112 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7225159ea5dafd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d516630c67afd565</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Scientist, Repair Order (RO) Duration Analytics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63b9d56f94df8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a455a483afe8350a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Capgemini Invent - Contextual Systems Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7de96313bda682b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cbd8e5fda7c2377</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949dc07e149530ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a00ba81a52a3506e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Computer Vision Engineer-Edge</t>
+          <t>Cloud Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viatouch Media Inc</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, MLflow, Git, Python, R, Optimization</t>
+          <t>RAG, Glue, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7148302e3316ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c04f106fe6e2d145</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>Cloud Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, Glue, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc744e38f33256f</t>
+          <t>https://www.indeed.com/viewjob?jk=101d501682b81b7d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer / FrontEnd Engineer, Qualcomm AI SW Stack</t>
+          <t>Senior Mobile Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363d9afb96af951b</t>
+          <t>https://www.indeed.com/viewjob?jk=f09eeb412a13ea9d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Core AI Software</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ff71f1c106957f</t>
+          <t>https://www.indeed.com/viewjob?jk=c302d85236b05243</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer- ETL/Python/Pyspark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,637 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bc95b3eeb8d40</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Engineer Contractor - Talent Reserve (contract)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, PySpark, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35a1544e260ab8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51e94afb6f8a79f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e64b465c8e84bf56</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29dea18cde3fa715</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dev Ops Engineer - Project Delivery Specialist Analyst</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9940bae2a9c7dc6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Ignition Platform Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f264960d10992dc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Capgemini Invent - Contextual Systems Engineer Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4aa0383c6ea6e83</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>GenAI Software Development Architect</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6d8b3ddffcbfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer – Google ADK/GCP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>TTEC Digital</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5aaa66d5e404832</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f03558ae01650be1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2751e712d2e52966</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SCADA Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f560305e16d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior SCADA Engineer - Ignition Platform</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c99fad1f2660ef7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b25219457e0314cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Mochi Health</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc44245d474ec216</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI and GTM Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43d514bb5b64d772</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AI and GTM Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf1042f78fc6b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BI Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Spire Orthopedic Partners</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Athena, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97ca3daded6ed547</t>
+          <t>https://www.indeed.com/viewjob?jk=f52fd2442fd01339</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Open Access Technology International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,287 +496,147 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e66310e18f4395c</t>
+          <t>https://www.indeed.com/viewjob?jk=287537cb95007a53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Data Scientist, RAG, Copilot, S3, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Scientist</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa36a7fae06cb300</t>
+          <t>https://www.indeed.com/viewjob?jk=53d30893c6d70cfe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Shopware Architect/Senior Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Site Technologies</t>
+          <t>Americaneagle.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9280dd7fbca926ff</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer / Sr. Data Engineer (Big Query)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>DEPT OF PARKS &amp; RECREATION</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, AKS, BigQuery, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a591df5e800f937b</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GenAI Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=248126d78ad5b9b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Scientist, AI for Biomedical Imaging</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Copilot, Hugging Face, PyTorch, OpenCV, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6644ad8b7dede843</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f32e83eb3499e290</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa26ce55fa5c61b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca2ab85f9949f01</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open Access Technology International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287537cb95007a53</t>
+          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2a4a548edfa2d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d30893c6d70cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=083d9f7d08d3a408</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shopware Architect/Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Americaneagle.com</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,1232 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9280dd7fbca926ff</t>
+          <t>https://www.indeed.com/viewjob?jk=51777e526ce81231</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEPT OF PARKS &amp; RECREATION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c748fc1875cf9fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Product Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bristol, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, S3, EC2, Docker, CI/CD, Git, Kafka, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eff3a46155c05ef2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TDS Global Solutions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AABM Clouds Data Solutions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73c6029c853b122e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr. AI Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Restaurant Brands International</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supply Chain Business Analyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19070dba73bb1c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, CI/CD, Git, Databricks, PySpark, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Biomedical Data Statistician, Technical Assistant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The University of Chicago</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, MySQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fd1615566eef286</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer / API Integration Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The McPherson Companies, Inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trussville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=144850734ed658b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad5c7561f8107046</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f9a3b02ea4f8411</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5878843f3a313245</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97e5b60918d8761e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8e317d8c73eed67</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cda143dd6f7aa2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43fc93502cb483cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70c7a014bf13fcd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b61d6ff960df0d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=790c62158764df2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d45fc6880f8de4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d08ab8c0fd2fd7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f2b8018e4404b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f16c88df676ccda</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b9efcb90cf9bf90</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae060a4ace06f60a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f17ad8ddac2f1c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33418ab6f3cd44f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Taylor, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d7751276d873524</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>The University of Chicago</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca2ab85f9949f01</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Hadoop, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef27c99008bf1506</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The Friedkin Group</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, FastAPI, CI/CD, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0504d6258897ecea</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Signifyd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Databricks, Cassandra, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f382ac64e9ad7889</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SGN Global Technologies</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=598884f00e282903</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ab42313e64889f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist - Decision Analytics</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dfcfd1faab38caf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, S3, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d71e12d841637c39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2a4a548edfa2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083d9f7d08d3a408</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc7461f2e21a8b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
+          <t>RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51777e526ce81231</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Platform Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c748fc1875cf9fb</t>
+          <t>https://www.indeed.com/viewjob?jk=00e7e05572f1f556</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Consultant Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, EC2, Docker, CI/CD, Git, Kafka, MySQL, SQL</t>
+          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff3a46155c05ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5612b97ea8c489f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Senior Software Engineer (Limited-Term)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Univeristy Of Colorado Boulder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f6ded9a00cc9da</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Engineer, AI-Accelerated Application &amp; Systems Development</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AABM Clouds Data Solutions</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c6029c853b122e</t>
+          <t>https://www.indeed.com/viewjob?jk=f138d1e77f478ada</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Advisory AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>AI Engineer, RAG, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=714042154ba31a6a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Supply Chain Business Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>RIB Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Synapse, Data Lake, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Synapse, CI/CD, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19070dba73bb1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c05fe11839621</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Git, Databricks, PySpark, Hadoop, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=51158e2ca8992b9e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Biomedical Data Statistician, Technical Assistant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, MySQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1615566eef286</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2e60a2079e4e94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Full-Stack Developer - Platform Services SMTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>RAG, Kinesis, Terraform, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=77306632aba3d62a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer II, Fulfillment</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Taskrabbit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, CI/CD, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144850734ed658b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3888649101820d7c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior OpenStack DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Five9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5c7561f8107046</t>
+          <t>https://www.indeed.com/viewjob?jk=3db799ac8edfc8df</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Scientist - GenAI/NLP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Maryland City, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Copilot, Mistral, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9a3b02ea4f8411</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c4b219d2567fb9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Scientist - GenAI/NLP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Copilot, Mistral, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,777 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5878843f3a313245</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97e5b60918d8761e</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e317d8c73eed67</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cda143dd6f7aa2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43fc93502cb483cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70c7a014bf13fcd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b61d6ff960df0d73</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=790c62158764df2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d45fc6880f8de4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d08ab8c0fd2fd7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2b8018e4404b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f16c88df676ccda</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9efcb90cf9bf90</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae060a4ace06f60a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f17ad8ddac2f1c30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33418ab6f3cd44f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Samsung Electronics</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Taylor, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d7751276d873524</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>The University of Chicago</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Hadoop, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef27c99008bf1506</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Full Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, FastAPI, CI/CD, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0504d6258897ecea</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Signifyd</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Databricks, Cassandra, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f382ac64e9ad7889</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SGN Global Technologies</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=598884f00e282903</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab42313e64889f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist - Decision Analytics</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfcfd1faab38caf</t>
+          <t>https://www.indeed.com/viewjob?jk=a95f4f531ccc0227</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, S3, FastAPI, CI/CD</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71e12d841637c39</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc7461f2e21a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0323019ff41585</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Git, BigQuery, Python, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=5573e25f20e0c521</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Platform Software Engineer</t>
+          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e7e05572f1f556</t>
+          <t>https://www.indeed.com/viewjob?jk=77347b35a6b839b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consultant Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+          <t>BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5612b97ea8c489f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Limited-Term)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Univeristy Of Colorado Boulder</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, Dataflow, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f6ded9a00cc9da</t>
+          <t>https://www.indeed.com/viewjob?jk=b399e7f3ef8c31e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, AI-Accelerated Application &amp; Systems Development</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f138d1e77f478ada</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Advisory AI Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714042154ba31a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RIB Software</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Synapse, CI/CD, Git, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c05fe11839621</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51158e2ca8992b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2e60a2079e4e94</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Platform Services SMTS</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Terraform, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77306632aba3d62a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fulfillment</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java, A/B Testing</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3888649101820d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior OpenStack DevOps Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Five9</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db799ac8edfc8df</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/NLP</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Maryland City, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Copilot, Mistral, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,672 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c4b219d2567fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/NLP</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>System Engineer - Automation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Moxie Pest Control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stevens Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hoboken, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=155010e5cafdc3d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Tiger Analytics</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Information Technology - Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Marana Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marana, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Athena, Synapse, Data Lake, Dataflow, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer (.NET / Python)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Common Objects</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PyTorch, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4451ac238f2e3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Datavault AI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41cc62daef64881a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>City of Hope</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dacefce2d1cb069</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa4242f8828cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Computer Vision Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CargoMatrix Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hewlett, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=325f706bd80458b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pegasystems</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dulles, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692c027c21e3b84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Java Backend developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Copilot, Mistral, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95f4f531ccc0227</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Git, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I – AI &amp; Model Monitoring</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unum</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=297d47100da33a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technical Solutioning Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AIG</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93b01fb8a6ea7402</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Technical Solutioning Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AIG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=688e3b33fad034fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pantherx Specialty Llc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer – Infra Services</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Five9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4223c44c321ec09b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Integration &amp; Test Systems Engineer (Epsilon3 Developer)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Midland, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db4abe8351841757</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-10.xlsx
+++ b/daily_matches/job_matches_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Redshift, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0323019ff41585</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed93842343d38d1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
+          <t>RAG, S3, Redshift, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5573e25f20e0c521</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend (Lake Analytics Platform)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
+          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77347b35a6b839b3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9015d7a37c3430</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>DevOps Engineer 3 (Sr DevSec Engineer)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Black Duck Software</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, PySpark, Tableau, Power BI</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=2755d105fb794cdd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, Dataflow, BigQuery</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b399e7f3ef8c31e6</t>
+          <t>https://www.indeed.com/viewjob?jk=426c34fade31c3a8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Engineer, AI - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Dormont Manufacturing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d63b1bf3deceb9c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Engineer, AI - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e386b9dd5fbab18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Production Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=59ee8f96cee196a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=9e96699ac18ea124</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Docker, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9fe9a74a9651a35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Kafka, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=d8652b0db882778d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, Kubernetes, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Risk Management - Data Scientist Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, TensorFlow, PyTorch, Git, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=af8fee6fce694d96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=413b032eb64e16a2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Associate – Software Development Engineer, Procurement Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Snowflake, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=e571bf79193ac34d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>Software Quality Assurance Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prompt Engineering, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=48b66abe5bb6d646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=155010e5cafdc3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=859582360a5d861c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>MMGY Global</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=4d009fd94e3385e2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Athena, Synapse, Data Lake, Dataflow, Databricks, Power BI, SQL, R, Scala</t>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,462 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer (.NET / Python)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Common Objects</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PyTorch, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c4451ac238f2e3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Datavault AI</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41cc62daef64881a</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist - Remote</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>City of Hope</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dacefce2d1cb069</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4242f8828cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Computer Vision Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CargoMatrix Inc.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Hewlett, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=325f706bd80458b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Pegasystems</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Dulles, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=692c027c21e3b84a</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Java Backend developer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, Git, Cassandra, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst I – AI &amp; Model Monitoring</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Unum</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=297d47100da33a4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Technical Solutioning Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93b01fb8a6ea7402</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Technical Solutioning Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688e3b33fad034fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Pantherx Specialty Llc</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer – Infra Services</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Five9</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c44c321ec09b</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Integration &amp; Test Systems Engineer (Epsilon3 Developer)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Midland, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db4abe8351841757</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfedbdb4f35134d</t>
         </is>
       </c>
     </row>
